--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-10-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-10-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4933A082-0762-42B7-95C0-6FF4DB959692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3AE41A-DFDA-4D85-AF08-F1690427D58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -231,13 +231,6 @@
 linh kiện dùng cho sửa chữa)</t>
   </si>
   <si>
-    <t>PHIẾU TÍNH CHIẾT KHẤU THÁNG 09 NĂM 2026</t>
-  </si>
-  <si>
-    <t>PHIẾU XÁC NHẬN TỒN 
-SẢN XUẤT THÁNG 09 - 2026</t>
-  </si>
-  <si>
     <t>Card Reader (old version)</t>
   </si>
   <si>
@@ -272,6 +265,13 @@
   </si>
   <si>
     <t>Tồn lô 5 VNSH03, 9 thiết bị lỗi</t>
+  </si>
+  <si>
+    <t>PHIẾU XÁC NHẬN TỒN 
+SẢN XUẤT THÁNG 10 - 2026</t>
+  </si>
+  <si>
+    <t>PHIẾU TÍNH CHIẾT KHẤU THÁNG 10 NĂM 2026</t>
   </si>
 </sst>
 </file>
@@ -814,6 +814,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1031,9 +1034,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1064,7 +1064,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1229142</xdr:colOff>
+      <xdr:colOff>1138033</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>26922</xdr:rowOff>
     </xdr:to>
@@ -1119,7 +1119,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1702490</xdr:colOff>
+      <xdr:colOff>1449457</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>189640</xdr:rowOff>
     </xdr:to>
@@ -1151,7 +1151,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="130865" y="186360"/>
-          <a:ext cx="2184538" cy="384280"/>
+          <a:ext cx="1931505" cy="384280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1511,83 +1511,83 @@
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
     <col min="4" max="4" width="20.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="81"/>
-      <c r="B1" s="82"/>
-      <c r="C1" s="89" t="s">
+      <c r="A1" s="82"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="86" t="s">
+      <c r="A2" s="82"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="89"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="94" t="s">
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="97"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83" t="s">
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="86"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
+      <c r="A5" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="93"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="40"/>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
       <c r="D6" s="41"/>
-      <c r="E6" s="91" t="str">
+      <c r="E6" s="92" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 10 năm 2026</v>
       </c>
-      <c r="F6" s="91"/>
+      <c r="F6" s="92"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
       <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" s="24">
         <v>450</v>
@@ -1670,8 +1670,8 @@
       <c r="A13" s="24">
         <v>3</v>
       </c>
-      <c r="B13" s="150" t="s">
-        <v>78</v>
+      <c r="B13" s="76" t="s">
+        <v>76</v>
       </c>
       <c r="C13" s="24">
         <v>100</v>
@@ -1689,8 +1689,8 @@
       <c r="A14" s="24">
         <v>4</v>
       </c>
-      <c r="B14" s="150" t="s">
-        <v>79</v>
+      <c r="B14" s="76" t="s">
+        <v>77</v>
       </c>
       <c r="C14" s="24">
         <v>57</v>
@@ -1705,10 +1705,10 @@
       <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="76" t="s">
+      <c r="A15" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="77"/>
+      <c r="B15" s="78"/>
       <c r="C15" s="28">
         <f>SUM(C11:C14)</f>
         <v>1107</v>
@@ -1718,12 +1718,12 @@
       <c r="F15" s="24"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="78" t="s">
+      <c r="A16" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
       <c r="E16" s="27">
         <f>SUM(E11:E14)</f>
         <v>5992000</v>
@@ -1747,33 +1747,33 @@
       <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="79" t="s">
+      <c r="A19" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="79"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="79" t="s">
+      <c r="D19" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="79"/>
+      <c r="E19" s="80"/>
       <c r="F19" s="58" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="80"/>
+      <c r="B20" s="81"/>
       <c r="C20" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="80" t="s">
+      <c r="D20" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="80"/>
+      <c r="E20" s="81"/>
       <c r="F20" s="17" t="s">
         <v>6</v>
       </c>
@@ -1811,17 +1811,17 @@
       <c r="F24" s="38"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="79" t="s">
+      <c r="A25" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="79"/>
+      <c r="B25" s="80"/>
       <c r="C25" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="79" t="s">
+      <c r="D25" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="79"/>
+      <c r="E25" s="80"/>
       <c r="F25" s="58" t="s">
         <v>8</v>
       </c>
@@ -1892,7 +1892,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="28.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" style="1" customWidth="1"/>
@@ -1908,64 +1908,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="101"/>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103" t="s">
+      <c r="A1" s="102"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="112" t="s">
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="115"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="101"/>
-      <c r="B3" s="102"/>
-      <c r="C3" s="94" t="s">
+      <c r="A3" s="102"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="97"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="83" t="s">
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="86"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="104" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107"/>
+      <c r="A5" s="105" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="106"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="108"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45"/>
@@ -1976,7 +1976,7 @@
       <c r="F6" s="33"/>
       <c r="G6" s="33"/>
       <c r="H6" s="33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2014,10 +2014,10 @@
       <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="108" t="s">
+      <c r="A10" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="109"/>
+      <c r="B10" s="110"/>
       <c r="C10" s="26">
         <f>'Bảng tính CK'!E16</f>
         <v>5992000</v>
@@ -2029,10 +2029,10 @@
       <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="97" t="s">
+      <c r="A11" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="98"/>
+      <c r="B11" s="99"/>
       <c r="C11" s="26">
         <v>3</v>
       </c>
@@ -2043,10 +2043,10 @@
       <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="111"/>
+      <c r="B12" s="112"/>
       <c r="C12" s="24">
         <v>0</v>
       </c>
@@ -2057,13 +2057,13 @@
       <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="99" t="s">
+      <c r="A13" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="100"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="24">
         <f>COUNTIFS(C16:C19, "&gt;=2.5",C16:C19,"&lt;7")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
@@ -2118,11 +2118,11 @@
         <v>0</v>
       </c>
       <c r="D16" s="53">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="E16" s="26">
         <f>($C$10*D16)/$D$19</f>
-        <v>1997333.3333333333</v>
+        <v>2097200</v>
       </c>
       <c r="F16" s="26">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H16" s="26">
         <f>((E16-F16)+($F$20/10))-G16</f>
-        <v>1997333.3333333333</v>
+        <v>2097200</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2143,14 +2143,14 @@
         <v>25</v>
       </c>
       <c r="C17" s="25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="53">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="E17" s="26">
         <f>($C$10*D17)/$D$19</f>
-        <v>1997333.3333333333</v>
+        <v>2097200</v>
       </c>
       <c r="F17" s="26">
         <v>0</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H17" s="26">
         <f>((E17-F17)+($F$20/10))-G17</f>
-        <v>1997333.3333333333</v>
+        <v>2097200</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2171,14 +2171,14 @@
         <v>19</v>
       </c>
       <c r="C18" s="25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D18" s="53">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E18" s="26">
         <f>($C$10*D18)/$D$19</f>
-        <v>1997333.3333333333</v>
+        <v>1797600</v>
       </c>
       <c r="F18" s="26">
         <v>0</v>
@@ -2188,15 +2188,15 @@
       </c>
       <c r="H18" s="26">
         <f>((E18-F18)+($F$20/10))-G18</f>
-        <v>1997333.3333333333</v>
+        <v>1797600</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="115" t="s">
+      <c r="A19" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="116"/>
-      <c r="C19" s="117"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="118"/>
       <c r="D19" s="54">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2207,11 +2207,11 @@
       <c r="H19" s="26"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="118"/>
-      <c r="C20" s="77"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="78"/>
       <c r="D20" s="19"/>
       <c r="E20" s="27">
         <f>SUM(E16:E18)</f>
@@ -2254,40 +2254,40 @@
       <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="79" t="s">
+      <c r="A23" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79" t="s">
+      <c r="B23" s="80"/>
+      <c r="C23" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="119" t="s">
+      <c r="D23" s="80"/>
+      <c r="E23" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="119"/>
-      <c r="G23" s="79" t="s">
+      <c r="F23" s="120"/>
+      <c r="G23" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="79"/>
+      <c r="H23" s="80"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80" t="s">
+      <c r="B24" s="81"/>
+      <c r="C24" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="80"/>
-      <c r="E24" s="120" t="s">
+      <c r="D24" s="81"/>
+      <c r="E24" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="120"/>
-      <c r="G24" s="80" t="s">
+      <c r="F24" s="121"/>
+      <c r="G24" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="80"/>
+      <c r="H24" s="81"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="31"/>
@@ -2330,22 +2330,22 @@
       <c r="H28" s="32"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79" t="s">
+      <c r="B29" s="80"/>
+      <c r="C29" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="79"/>
-      <c r="E29" s="119" t="s">
+      <c r="D29" s="80"/>
+      <c r="E29" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="119"/>
-      <c r="G29" s="79" t="s">
+      <c r="F29" s="120"/>
+      <c r="G29" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="79"/>
+      <c r="H29" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2402,55 +2402,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="130"/>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="131" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="137" t="s">
+      <c r="A1" s="131"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="132" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="138"/>
+      <c r="H1" s="139"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="130"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="137" t="s">
+      <c r="A2" s="131"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="138"/>
+      <c r="H2" s="139"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="130"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="137" t="s">
+      <c r="A3" s="131"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="138"/>
+      <c r="H3" s="139"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="129" t="str">
+      <c r="A4" s="130" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 31 tháng 10 năm 2026</v>
       </c>
-      <c r="B4" s="129"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
@@ -2487,27 +2487,27 @@
       <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="123" t="s">
+      <c r="B8" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="125" t="s">
+      <c r="C8" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="128" t="s">
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="129" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="128"/>
+      <c r="H8" s="129"/>
       <c r="I8" s="30"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="124"/>
-      <c r="B9" s="124"/>
+      <c r="A9" s="125"/>
+      <c r="B9" s="125"/>
       <c r="C9" s="70" t="s">
         <v>59</v>
       </c>
@@ -2520,8 +2520,8 @@
       <c r="F9" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
       <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2544,10 +2544,10 @@
         <f>D10-E10</f>
         <v>2</v>
       </c>
-      <c r="G10" s="121" t="s">
+      <c r="G10" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="122"/>
+      <c r="H10" s="123"/>
       <c r="I10" s="30"/>
     </row>
     <row r="11" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2570,10 +2570,10 @@
         <f>SUM(D11-E11)</f>
         <v>11</v>
       </c>
-      <c r="G11" s="121" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="122"/>
+      <c r="G11" s="122" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="123"/>
       <c r="I11" s="30"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2596,16 +2596,16 @@
         <f>SUM(D12-E12)</f>
         <v>2050</v>
       </c>
-      <c r="G12" s="121" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="122"/>
+      <c r="G12" s="122" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="123"/>
       <c r="I12" s="30"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="51"/>
       <c r="B13" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="21">
         <v>700</v>
@@ -2620,10 +2620,10 @@
         <f>SUM(D13-E13)</f>
         <v>400</v>
       </c>
-      <c r="G13" s="121" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13" s="122"/>
+      <c r="G13" s="122" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="123"/>
       <c r="I13" s="30"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2646,10 +2646,10 @@
         <f>D14-E14</f>
         <v>2</v>
       </c>
-      <c r="G14" s="144" t="s">
+      <c r="G14" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="144"/>
+      <c r="H14" s="145"/>
       <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2672,10 +2672,10 @@
         <f t="shared" ref="F15" si="0">D15</f>
         <v>178</v>
       </c>
-      <c r="G15" s="144" t="s">
+      <c r="G15" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="144"/>
+      <c r="H15" s="145"/>
       <c r="I15" s="30"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2698,10 +2698,10 @@
         <f>D16-E16</f>
         <v>52</v>
       </c>
-      <c r="G16" s="144" t="s">
+      <c r="G16" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="144"/>
+      <c r="H16" s="145"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
@@ -2723,10 +2723,10 @@
         <f>D17-E17</f>
         <v>22</v>
       </c>
-      <c r="G17" s="144" t="s">
+      <c r="G17" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="144"/>
+      <c r="H17" s="145"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="51">
@@ -2748,10 +2748,10 @@
         <f>D18-E18</f>
         <v>2</v>
       </c>
-      <c r="G18" s="144" t="s">
+      <c r="G18" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="144"/>
+      <c r="H18" s="145"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
@@ -2772,10 +2772,10 @@
       <c r="F19" s="23">
         <v>3</v>
       </c>
-      <c r="G19" s="144" t="s">
+      <c r="G19" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="144"/>
+      <c r="H19" s="145"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="51">
@@ -2793,10 +2793,10 @@
         <f>SUM(D20-E20)</f>
         <v>-57</v>
       </c>
-      <c r="G20" s="145" t="s">
+      <c r="G20" s="146" t="s">
         <v>66</v>
       </c>
-      <c r="H20" s="146"/>
+      <c r="H20" s="147"/>
     </row>
     <row r="21" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="51"/>
@@ -2816,10 +2816,10 @@
         <f>SUM(D21-E21)</f>
         <v>1</v>
       </c>
-      <c r="G21" s="143" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="143"/>
+      <c r="G21" s="144" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="144"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
@@ -2841,16 +2841,16 @@
         <f>SUM(D22-E22)</f>
         <v>480</v>
       </c>
-      <c r="G22" s="143" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="143"/>
+      <c r="G22" s="144" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="144"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="139" t="s">
+      <c r="A23" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="140"/>
+      <c r="B23" s="141"/>
       <c r="C23" s="52">
         <f>SUM(C10:C22)</f>
         <v>8160</v>
@@ -2867,8 +2867,8 @@
         <f>SUM(F10:F22)</f>
         <v>3146</v>
       </c>
-      <c r="G23" s="141"/>
-      <c r="H23" s="142"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="143"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="65"/>
@@ -2881,40 +2881,40 @@
       <c r="H24" s="65"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="149" t="s">
+      <c r="A25" s="150" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="149"/>
-      <c r="C25" s="149" t="s">
+      <c r="B25" s="150"/>
+      <c r="C25" s="150" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149" t="s">
+      <c r="D25" s="150"/>
+      <c r="E25" s="150" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="149"/>
-      <c r="G25" s="79" t="s">
+      <c r="F25" s="150"/>
+      <c r="G25" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="H25" s="79"/>
+      <c r="H25" s="80"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="148" t="s">
+      <c r="A26" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="148"/>
-      <c r="C26" s="148" t="s">
+      <c r="B26" s="149"/>
+      <c r="C26" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148" t="s">
+      <c r="D26" s="149"/>
+      <c r="E26" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148" t="s">
+      <c r="F26" s="149"/>
+      <c r="G26" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="H26" s="148"/>
+      <c r="H26" s="149"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="71"/>
@@ -2957,22 +2957,22 @@
       <c r="H30" s="73"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="147" t="s">
+      <c r="A31" s="148" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="147"/>
-      <c r="C31" s="147" t="s">
+      <c r="B31" s="148"/>
+      <c r="C31" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="147"/>
-      <c r="E31" s="147" t="s">
+      <c r="D31" s="148"/>
+      <c r="E31" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="147"/>
-      <c r="G31" s="147" t="s">
+      <c r="F31" s="148"/>
+      <c r="G31" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="H31" s="147"/>
+      <c r="H31" s="148"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="65"/>
